--- a/JobOfferSolution/JO.BlazorDemoApp/wwwroot/excel/CandidateResponseSample.xlsx
+++ b/JobOfferSolution/JO.BlazorDemoApp/wwwroot/excel/CandidateResponseSample.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unitedlaboratoriesinc-my.sharepoint.com/personal/c_relaude_unilab_com_ph1/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F728291E-94E9-4FA6-ACB8-27C075A2D7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{F728291E-94E9-4FA6-ACB8-27C075A2D7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{334598A1-A56E-42C6-8799-6A34672128A9}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4FD2D0AE-4E76-4D1A-AF79-DA48DD428EC5}"/>
+    <workbookView xWindow="27456" yWindow="2016" windowWidth="18996" windowHeight="10512" xr2:uid="{4FD2D0AE-4E76-4D1A-AF79-DA48DD428EC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="120">
   <si>
     <t>Id</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Cellular Phone</t>
   </si>
   <si>
-    <t>anonymous</t>
-  </si>
-  <si>
     <t>I agree</t>
   </si>
   <si>
@@ -381,16 +378,45 @@
   </si>
   <si>
     <t>Na</t>
+  </si>
+  <si>
+    <t>Candidate DBoxID</t>
+  </si>
+  <si>
+    <t>2025-02-01</t>
+  </si>
+  <si>
+    <t>2025-02-02</t>
+  </si>
+  <si>
+    <t>jkim@mail.com</t>
+  </si>
+  <si>
+    <t>hpham@mail.com</t>
+  </si>
+  <si>
+    <t>jdcruz@mail.com</t>
+  </si>
+  <si>
+    <t>rpaloma@mail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -413,13 +439,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -752,679 +782,716 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E9C3992-F8BC-4212-8582-5FBA4DB6E60E}">
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AV5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="145.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="28.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="40.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="24.54296875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="43.453125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="35.26953125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27.08984375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="67.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="76.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="50.26953125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="42" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="32.54296875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="33.6328125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="24.90625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="31.6328125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="38.36328125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="41.26953125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="32.26953125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="23.36328125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="47.54296875" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="35.54296875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="145.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="40.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="43.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="35.26953125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="27.08984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="67.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="76.54296875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="50.26953125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="42" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="50.7265625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="33.6328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="31.6328125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="38.36328125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="29.6328125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="47.54296875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2</v>
       </c>
       <c r="B2">
-        <v>45689.612858796296</v>
-      </c>
-      <c r="C2">
-        <v>45689.615590277775</v>
-      </c>
-      <c r="D2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G2" t="s">
         <v>47</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>48</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J2" t="s">
         <v>49</v>
       </c>
-      <c r="H2">
-        <v>45689</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="L2">
+        <v>44000</v>
+      </c>
+      <c r="M2" t="s">
         <v>50</v>
       </c>
-      <c r="K2">
-        <v>44000</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="N2" t="s">
         <v>51</v>
       </c>
-      <c r="M2" t="s">
+      <c r="O2" t="s">
         <v>52</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>53</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>54</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2">
+        <v>22000</v>
+      </c>
+      <c r="T2" t="s">
         <v>56</v>
       </c>
-      <c r="R2">
+      <c r="U2" t="s">
+        <v>57</v>
+      </c>
+      <c r="V2">
+        <v>10000</v>
+      </c>
+      <c r="W2" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2">
+        <v>3000</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z2">
+        <v>8000</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>36000</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI2">
         <v>22000</v>
       </c>
-      <c r="S2" t="s">
-        <v>57</v>
-      </c>
-      <c r="T2" t="s">
-        <v>58</v>
-      </c>
-      <c r="U2">
-        <v>10000</v>
-      </c>
-      <c r="V2" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2">
-        <v>3000</v>
-      </c>
-      <c r="X2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y2">
-        <v>8000</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>36000</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AJ2" t="s">
         <v>65</v>
       </c>
-      <c r="AH2">
-        <v>22000</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AK2" t="s">
         <v>66</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" t="s">
         <v>67</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AM2" t="s">
         <v>68</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AN2" t="s">
         <v>69</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AP2" t="s">
         <v>70</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AQ2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR2" t="s">
         <v>71</v>
       </c>
-      <c r="AP2" t="s">
-        <v>71</v>
-      </c>
-      <c r="AQ2" t="s">
+      <c r="AS2" t="s">
         <v>72</v>
       </c>
-      <c r="AR2" t="s">
-        <v>73</v>
-      </c>
     </row>
-    <row r="3" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>3</v>
       </c>
       <c r="B3">
-        <v>45689.628935185188</v>
-      </c>
-      <c r="C3">
-        <v>45689.631585648145</v>
-      </c>
-      <c r="D3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" t="s">
         <v>47</v>
       </c>
-      <c r="F3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J3" t="s">
         <v>74</v>
       </c>
-      <c r="H3">
-        <v>45689</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>75</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3">
+        <v>40000</v>
+      </c>
+      <c r="M3" t="s">
         <v>76</v>
       </c>
-      <c r="K3">
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>79</v>
+      </c>
+      <c r="R3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S3">
         <v>40000</v>
       </c>
-      <c r="L3" t="s">
-        <v>77</v>
-      </c>
-      <c r="M3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" t="s">
-        <v>78</v>
-      </c>
-      <c r="O3" t="s">
-        <v>79</v>
-      </c>
-      <c r="P3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="T3" t="s">
+        <v>56</v>
+      </c>
+      <c r="U3" t="s">
+        <v>57</v>
+      </c>
+      <c r="V3">
+        <v>10000</v>
+      </c>
+      <c r="W3" t="s">
+        <v>58</v>
+      </c>
+      <c r="X3">
+        <v>4000</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z3">
+        <v>8000</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB3" t="s">
         <v>81</v>
       </c>
-      <c r="R3">
-        <v>40000</v>
-      </c>
-      <c r="S3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" t="s">
-        <v>58</v>
-      </c>
-      <c r="U3">
-        <v>10000</v>
-      </c>
-      <c r="V3" t="s">
-        <v>59</v>
-      </c>
-      <c r="W3">
-        <v>4000</v>
-      </c>
-      <c r="X3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y3">
-        <v>8000</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>82</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AD3">
+        <v>7000</v>
+      </c>
+      <c r="AE3">
+        <v>35000</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI3">
+        <v>23000</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AS3" t="s">
         <v>83</v>
       </c>
-      <c r="AC3">
-        <v>7000</v>
-      </c>
-      <c r="AD3">
-        <v>35000</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH3">
-        <v>23000</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>84</v>
-      </c>
     </row>
-    <row r="4" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>45689.6738541667</v>
-      </c>
-      <c r="C4">
-        <v>45689.677465277797</v>
-      </c>
-      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" t="s">
         <v>47</v>
       </c>
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" t="s">
         <v>85</v>
       </c>
-      <c r="H4">
-        <v>45696</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>86</v>
       </c>
-      <c r="J4" t="s">
+      <c r="L4">
+        <v>50000</v>
+      </c>
+      <c r="M4" t="s">
         <v>87</v>
       </c>
-      <c r="K4">
-        <v>50000</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="N4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O4" t="s">
         <v>88</v>
       </c>
-      <c r="M4" t="s">
-        <v>52</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="P4" t="s">
         <v>89</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>90</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>91</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="S4">
+        <v>40000</v>
+      </c>
+      <c r="T4" t="s">
         <v>92</v>
       </c>
-      <c r="R4">
-        <v>40000</v>
-      </c>
-      <c r="S4" t="s">
+      <c r="U4" t="s">
+        <v>62</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
         <v>93</v>
       </c>
-      <c r="T4" t="s">
+      <c r="X4">
+        <v>2000</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z4">
+        <v>8000</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB4">
+        <v>1500</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD4">
+        <v>12000</v>
+      </c>
+      <c r="AE4">
+        <v>60000</v>
+      </c>
+      <c r="AF4" t="s">
         <v>63</v>
       </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="AG4">
+        <v>80000</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI4">
+        <v>20000</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>94</v>
       </c>
-      <c r="W4">
-        <v>2000</v>
-      </c>
-      <c r="X4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y4">
-        <v>8000</v>
-      </c>
-      <c r="Z4" t="s">
+      <c r="AK4" t="s">
+        <v>95</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>96</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>97</v>
+      </c>
+      <c r="AN4" t="s">
         <v>61</v>
       </c>
-      <c r="AA4">
-        <v>1500</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>83</v>
-      </c>
-      <c r="AC4">
-        <v>12000</v>
-      </c>
-      <c r="AD4">
-        <v>60000</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AF4">
-        <v>80000</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>65</v>
-      </c>
-      <c r="AH4">
-        <v>20000</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>97</v>
-      </c>
-      <c r="AL4" t="s">
+      <c r="AO4" t="s">
         <v>98</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AP4" t="s">
+        <v>99</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>100</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>101</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AT4" t="s">
         <v>62</v>
       </c>
-      <c r="AN4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AO4" t="s">
-        <v>100</v>
-      </c>
-      <c r="AP4" t="s">
-        <v>101</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>102</v>
-      </c>
-      <c r="AR4" t="s">
+      <c r="AU4" t="s">
         <v>103</v>
       </c>
-      <c r="AS4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AT4" t="s">
+      <c r="AV4" t="s">
         <v>104</v>
       </c>
-      <c r="AU4" t="s">
-        <v>105</v>
-      </c>
     </row>
-    <row r="5" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:48" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>45690.496215277803</v>
-      </c>
-      <c r="C5">
-        <v>45690.5011689815</v>
-      </c>
-      <c r="D5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G5" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" t="s">
         <v>106</v>
       </c>
-      <c r="H5">
-        <v>45690</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>107</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5">
+        <v>40000</v>
+      </c>
+      <c r="M5" t="s">
+        <v>87</v>
+      </c>
+      <c r="N5" t="s">
+        <v>51</v>
+      </c>
+      <c r="O5" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" t="s">
         <v>108</v>
       </c>
-      <c r="K5">
+      <c r="Q5" t="s">
+        <v>79</v>
+      </c>
+      <c r="R5" t="s">
+        <v>109</v>
+      </c>
+      <c r="S5">
+        <v>48000</v>
+      </c>
+      <c r="T5" t="s">
+        <v>56</v>
+      </c>
+      <c r="U5" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5">
+        <v>5000</v>
+      </c>
+      <c r="W5" t="s">
+        <v>93</v>
+      </c>
+      <c r="X5">
+        <v>2000</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z5">
+        <v>8000</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>111</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
         <v>40000</v>
       </c>
-      <c r="L5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" t="s">
-        <v>89</v>
-      </c>
-      <c r="O5" t="s">
-        <v>109</v>
-      </c>
-      <c r="P5" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>110</v>
-      </c>
-      <c r="R5">
-        <v>48000</v>
-      </c>
-      <c r="S5" t="s">
-        <v>57</v>
-      </c>
-      <c r="T5" t="s">
-        <v>58</v>
-      </c>
-      <c r="U5">
-        <v>5000</v>
-      </c>
-      <c r="V5" t="s">
-        <v>94</v>
-      </c>
-      <c r="W5">
-        <v>2000</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="AF5" t="s">
         <v>111</v>
       </c>
-      <c r="Y5">
-        <v>8000</v>
-      </c>
-      <c r="Z5" t="s">
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="s">
         <v>112</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>40000</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>112</v>
-      </c>
-      <c r="AF5">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>113</v>
-      </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{BE4C3443-8A9E-4614-98F9-B899AE41ED1A}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{3CD75B3E-E74F-428D-8A00-89FCA8F87E3D}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{5F7B8B39-7C1F-4DDA-ACF0-1AF73630023B}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{5B9E6332-F770-4BC5-82A5-FD7F81465A7A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F2F0346F73F64E48BFC670CF2DCB7793" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f48527943eaa92f81f62586d434c4b1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="e24d20b8-254b-4473-ab6f-97d8d0808651" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a44a28048cc1bb517b4ed265ebbb4b2" ns3:_="">
     <xsd:import namespace="e24d20b8-254b-4473-ab6f-97d8d0808651"/>
@@ -1550,22 +1617,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D445C02-86FA-4AD1-A896-3C65F64976AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DAF5D1C-A650-46A9-9EAD-F938DA970924}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="e24d20b8-254b-4473-ab6f-97d8d0808651"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F80A68C6-ACE8-4D2D-A004-696A6076D052}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1581,28 +1657,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D445C02-86FA-4AD1-A896-3C65F64976AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DAF5D1C-A650-46A9-9EAD-F938DA970924}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="e24d20b8-254b-4473-ab6f-97d8d0808651"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>